--- a/data/final/ir_extraction.xlsx
+++ b/data/final/ir_extraction.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ23"/>
+  <dimension ref="A1:BZ27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>s13071_021_04706_5_kilifi_2013_2014</t>
+          <t>s13071_021_04706_5_pooled_gam</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -7977,7 +7977,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>33883000</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>journal_article</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -8000,17 +8000,17 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Anopheles gambiae (s.l.)</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Anopheles gambiae complex</t>
+          <t>An. gambiae complex</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Anopheles gambiae s.s.</t>
+          <t>An. gambiae s.s.</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -8020,12 +8020,12 @@
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>Kilifi County (eight sites: Ngombeni, Mbogolo, Jaribuni, Kidutani, Shibe, Mapawa, Mangororo, Burangi)</t>
+          <t>Kilifi County</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Kilifi County</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>larval dipping</t>
+          <t>larval collection</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -8280,7 +8280,7 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>PCR amplification of rDNA intergenic spacers</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="BW21" t="inlineStr">
         <is>
-          <t>3: Table 3 Knockdown resistance allelic frequency in An. gambiae (s.s.) populations from Kilifi county, coastal Kenya.</t>
+          <t>Table 3: Table 3 Knockdown resistance allelic frequency in An. gambiae (s.s.) populations from Kilifi county, coastal Kenya</t>
         </is>
       </c>
       <c r="BX21" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bioassay</t>
+          <t>genotype</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>s13071_021_04706_5_kilifi_2013_2014</t>
+          <t>s13071_021_04706_5_pooled_gam</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -8347,7 +8347,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>33883000</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -8360,7 +8360,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>journal_article</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -8370,17 +8370,17 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Anopheles gambiae (s.l.)</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Anopheles gambiae complex</t>
+          <t>An. gambiae complex</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Anopheles gambiae s.s.</t>
+          <t>An. gambiae s.s.</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -8390,12 +8390,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>Kilifi County (eight sites: Ngombeni, Mbogolo, Jaribuni, Kidutani, Shibe, Mapawa, Mangororo, Burangi)</t>
+          <t>Kilifi County</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Kilifi County</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -8450,12 +8450,12 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>larval dipping</t>
+          <t>larval collection</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>pyrethroids</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -8488,123 +8488,115 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>WHO tube bioassay</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AL22" t="n">
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>Vgsc</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>L995F</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>L1014F</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>real-time PCR</t>
+        </is>
+      </c>
+      <c r="AY22" t="n">
         <v>49</v>
       </c>
-      <c r="AM22" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO22" t="n">
-        <v>0.3061</v>
-      </c>
-      <c r="AP22" t="n">
-        <v>0.6939</v>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>confirmed resistance</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>24 h</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD22" t="n">
+        <v>49</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>1</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
@@ -8658,7 +8650,7 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>PCR amplification of rDNA intergenic spacers</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
@@ -8683,12 +8675,12 @@
       </c>
       <c r="BW22" t="inlineStr">
         <is>
-          <t>3: Upon exposure to pyrethroids for 24 h, a total of 15 An. gambiae, An. arabiensis and An. gambiae (s.s.) were identified with the resistant phenotype, while 34 had the susceptible phenotype.</t>
+          <t>and the 1014F kdr mutation was not detected in either An. gambiae (s.s.) or An. arabiensis.</t>
         </is>
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
@@ -8710,12 +8702,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>geno_pheno</t>
+          <t>bioassay</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>s13071_021_04706_5_kilifi_2013_2014</t>
+          <t>s13071_021_04706_5_burangi</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -8725,7 +8717,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>33883000</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -8738,7 +8730,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>primary</t>
+          <t>journal_article</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -8748,17 +8740,17 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Anopheles gambiae (s.l.)</t>
+          <t>Anopheles gambiae s.l.</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Anopheles gambiae complex</t>
+          <t>An. gambiae complex</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Anopheles gambiae s.s.</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -8768,42 +8760,38 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>Kilifi County (eight sites: Ngombeni, Mbogolo, Jaribuni, Kidutani, Shibe, Mapawa, Mangororo, Burangi)</t>
+          <t>Burangi</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Kilifi County</t>
+          <t>Kilifi</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+          <t>Malindi</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>-3.09828</v>
+      </c>
+      <c r="R23" t="n">
+        <v>40.04817</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>reported</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>p. 2</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>admin1</t>
+          <t>village</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -8828,12 +8816,12 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>larval dipping</t>
+          <t>larval collection</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -8847,21 +8835,21 @@
         </is>
       </c>
       <c r="AD23" t="n">
-        <v>49</v>
+        <v>500</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>pyrethroids</t>
+          <t>deltamethrin</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>type II</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
@@ -8871,12 +8859,12 @@
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>WHO tube bioassay</t>
+          <t>WHO tube</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>standard</t>
+          <t>susceptibility</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
@@ -8885,19 +8873,23 @@
         </is>
       </c>
       <c r="AL23" t="n">
-        <v>49</v>
-      </c>
-      <c r="AM23" t="n">
-        <v>15</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>34</v>
+        <v>100</v>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AO23" t="n">
-        <v>0.3061</v>
+        <v>0.545</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.6939</v>
+        <v>0.455</v>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
@@ -8911,12 +8903,12 @@
       </c>
       <c r="AS23" t="inlineStr">
         <is>
-          <t>Vgsc</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>L995S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -8939,67 +8931,95 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="AY23" t="n">
-        <v>49</v>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BA23" t="n">
-        <v>0.0612</v>
-      </c>
-      <c r="BB23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BC23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BD23" t="n">
-        <v>45</v>
-      </c>
-      <c r="BE23" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="BF23" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="BG23" t="n">
-        <v>0.9184</v>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>alive + dead</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
         <is>
-          <t>L995S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="BJ23" t="inlineStr">
         <is>
-          <t>L995S</t>
-        </is>
-      </c>
-      <c r="BK23" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM23" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN23" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO23" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP23" t="n">
-        <v>31</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
@@ -9008,7 +9028,7 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>PCR amplification of rDNA intergenic spacers</t>
+          <t>morphological</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
@@ -9018,35 +9038,1547 @@
       </c>
       <c r="BT23" t="inlineStr">
         <is>
+          <t>no (reported mortality only)</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>Deltamethrin resistance in An. gambiae (s.l.) was only recorded in one of the eight study sites (Burangi: n = 100, mortality 45.5%).</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bioassay</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5_burangi</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>10.1186/s13071-021-04706-5</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F24" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>p. 1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Anopheles gambiae s.l.</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>An. gambiae complex</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Burangi</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Malindi</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>-3.09828</v>
+      </c>
+      <c r="R24" t="n">
+        <v>40.04817</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>p. 2</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>village</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>2013-2014</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>multi-year</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>larval collection</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>adults</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>wild_reared</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>F0</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>permethrin</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>type I</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>0.75%</t>
+        </is>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>WHO tube</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>susceptibility</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AL24" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO24" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AQ24" t="inlineStr">
+        <is>
+          <t>confirmed resistance</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>24 h</t>
+        </is>
+      </c>
+      <c r="AS24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BF24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BI24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BJ24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BO24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BP24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BQ24" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BR24" t="inlineStr">
+        <is>
+          <t>morphological</t>
+        </is>
+      </c>
+      <c r="BS24" t="inlineStr">
+        <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="BU23" t="inlineStr">
+      <c r="BT24" t="inlineStr">
+        <is>
+          <t>no (reported mortality only)</t>
+        </is>
+      </c>
+      <c r="BU24" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="BV23" t="inlineStr">
+      <c r="BV24" t="inlineStr">
         <is>
           <t>FALSE</t>
         </is>
       </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>3: Table 3 Knockdown resistance allelic frequency in An. gambiae (s.s.) populations from Kilifi county, coastal Kenya. Resistant refers to mosquitoes alive after 24 h of exposure to pyrethroid pesticide.</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BY23" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="BZ23" t="inlineStr">
+      <c r="BW24" t="inlineStr">
+        <is>
+          <t>Coincidentally, permethrin resistance was also reported in the same study site (n = 100, mortality 48%).</t>
+        </is>
+      </c>
+      <c r="BX24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BY24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BZ24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>bioassay</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5_jaribuni</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>10.1186/s13071-021-04706-5</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F25" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>p. 1</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Anopheles gambiae s.l.</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>An. gambiae complex</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Jaribuni</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>-3.62054</v>
+      </c>
+      <c r="R25" t="n">
+        <v>39.73354</v>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>p. 2</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>village</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>2013-2014</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>multi-year</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>larval collection</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>adults</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>wild_reared</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>F0</t>
+        </is>
+      </c>
+      <c r="AD25" t="n">
+        <v>500</v>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>fenitrothion</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>not a pyrethroid</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>WHO tube</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>susceptibility</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AL25" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO25" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="AQ25" t="inlineStr">
+        <is>
+          <t>confirmed resistance</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>24 h</t>
+        </is>
+      </c>
+      <c r="AS25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BF25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BI25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BJ25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BO25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BP25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BQ25" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BR25" t="inlineStr">
+        <is>
+          <t>morphological</t>
+        </is>
+      </c>
+      <c r="BS25" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BT25" t="inlineStr">
+        <is>
+          <t>no (reported mortality only)</t>
+        </is>
+      </c>
+      <c r="BU25" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="BV25" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BW25" t="inlineStr">
+        <is>
+          <t>Adult mosquitoes were resistant to fenitrothion in Jaribuni (n = 100, mortality 88%)</t>
+        </is>
+      </c>
+      <c r="BX25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BY25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BZ25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>bioassay</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5_mbogolo</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>10.1186/s13071-021-04706-5</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>p. 1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Anopheles gambiae s.l.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>An. gambiae complex</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Mbogolo</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>-3.69806</v>
+      </c>
+      <c r="R26" t="n">
+        <v>39.81706</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>p. 2</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>village</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>2013-2014</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>multi-year</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>larval collection</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>adults</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>wild_reared</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>F0</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>455</v>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>bendiocarb</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>not a pyrethroid</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>WHO tube</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>susceptibility</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AL26" t="n">
+        <v>75</v>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO26" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AQ26" t="inlineStr">
+        <is>
+          <t>possible resistance</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>24 h</t>
+        </is>
+      </c>
+      <c r="AS26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BF26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BI26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BJ26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BO26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BP26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BQ26" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BR26" t="inlineStr">
+        <is>
+          <t>morphological</t>
+        </is>
+      </c>
+      <c r="BS26" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BT26" t="inlineStr">
+        <is>
+          <t>no (reported mortality only)</t>
+        </is>
+      </c>
+      <c r="BU26" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="BV26" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BW26" t="inlineStr">
+        <is>
+          <t>However, the possibility of resistance that requires further investigation was recorded against bendiocarb in Mbogolo (n = 75, mortality 93%)</t>
+        </is>
+      </c>
+      <c r="BX26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BY26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BZ26" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>bioassay</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>s13071_021_04706_5_ngombeni</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>10.1186/s13071-021-04706-5</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>journal_article</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>p. 1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Anopheles gambiae s.l.</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>An. gambiae complex</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Kenya</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Ngombeni</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Kilifi</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>-3.73208</v>
+      </c>
+      <c r="R27" t="n">
+        <v>39.76491</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>p. 2</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>village</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>2013-06</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>2014-07</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>2013-2014</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>multi-year</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>larval collection</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>adults</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>wild_reared</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>F0</t>
+        </is>
+      </c>
+      <c r="AD27" t="n">
+        <v>490</v>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>bendiocarb</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>not a pyrethroid</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>0.1%</t>
+        </is>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>WHO tube</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>susceptibility</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AL27" t="n">
+        <v>90</v>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="AQ27" t="inlineStr">
+        <is>
+          <t>possible resistance</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>24 h</t>
+        </is>
+      </c>
+      <c r="AS27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AV27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BA27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BB27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BC27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BE27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BF27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BG27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BI27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BJ27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BK27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BL27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BM27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BN27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BO27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BP27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BQ27" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BR27" t="inlineStr">
+        <is>
+          <t>morphological</t>
+        </is>
+      </c>
+      <c r="BS27" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="BT27" t="inlineStr">
+        <is>
+          <t>no (reported mortality only)</t>
+        </is>
+      </c>
+      <c r="BU27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="BV27" t="inlineStr">
+        <is>
+          <t>FALSE</t>
+        </is>
+      </c>
+      <c r="BW27" t="inlineStr">
+        <is>
+          <t>and Ng’ombeni (n = 90, mortality 97%).</t>
+        </is>
+      </c>
+      <c r="BX27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BY27" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="BZ27" t="inlineStr">
         <is>
           <t>NA</t>
         </is>

--- a/data/final/ir_extraction.xlsx
+++ b/data/final/ir_extraction.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BZ27"/>
+  <dimension ref="A1:CA27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -811,6 +811,11 @@
           <t>Supplementary material</t>
         </is>
       </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>Data quality flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1191,6 +1196,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1571,6 +1581,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1951,6 +1966,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2331,6 +2351,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2705,6 +2730,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3079,6 +3109,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3453,6 +3488,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3827,6 +3867,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4201,6 +4246,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4575,6 +4625,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -4949,6 +5004,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5323,6 +5383,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5697,6 +5762,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -6071,6 +6141,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -6445,6 +6520,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -6819,6 +6899,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -7199,6 +7284,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -7579,6 +7669,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -7953,6 +8048,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -8323,6 +8423,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -8693,6 +8798,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA22" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -9071,6 +9181,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -9449,6 +9564,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA24" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -9827,6 +9947,11 @@
           <t>NA</t>
         </is>
       </c>
+      <c r="CA25" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -10009,21 +10134,17 @@
       <c r="AL26" t="n">
         <v>75</v>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>5</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>70</v>
       </c>
       <c r="AO26" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.0667</v>
       </c>
       <c r="AP26" t="n">
-        <v>0.93</v>
+        <v>0.9333</v>
       </c>
       <c r="AQ26" t="inlineStr">
         <is>
@@ -10172,7 +10293,7 @@
       </c>
       <c r="BT26" t="inlineStr">
         <is>
-          <t>no (reported mortality only)</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU26" t="inlineStr">
@@ -10203,6 +10324,11 @@
       <c r="BZ26" t="inlineStr">
         <is>
           <t>NA</t>
+        </is>
+      </c>
+      <c r="CA26" t="inlineStr">
+        <is>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -10387,21 +10513,17 @@
       <c r="AL27" t="n">
         <v>90</v>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>87</v>
       </c>
       <c r="AO27" t="n">
-        <v>0.03</v>
+        <v>0.0333</v>
       </c>
       <c r="AP27" t="n">
-        <v>0.97</v>
+        <v>0.9667</v>
       </c>
       <c r="AQ27" t="inlineStr">
         <is>
@@ -10550,7 +10672,7 @@
       </c>
       <c r="BT27" t="inlineStr">
         <is>
-          <t>no (reported mortality only)</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU27" t="inlineStr">
@@ -10581,6 +10703,11 @@
       <c r="BZ27" t="inlineStr">
         <is>
           <t>NA</t>
+        </is>
+      </c>
+      <c r="CA27" t="inlineStr">
+        <is>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>

--- a/data/final/ir_extraction.xlsx
+++ b/data/final/ir_extraction.xlsx
@@ -825,12 +825,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>genotype</t>
+          <t>bioassay</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -883,21 +883,21 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Kribi urbain</t>
+          <t>Kribi rural</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>2.95</v>
+        <v>2.9167</v>
       </c>
       <c r="R2" t="n">
         <v>9.916700000000001</v>
@@ -914,7 +914,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -962,87 +962,77 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>permethrin</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>type I</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>WHO tube</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>diagnostic_dose</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AL2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>51</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.6375</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>0.3625</v>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>confirmed resistance</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>Vgsc</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>L995F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>L995F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
@@ -1052,24 +1042,28 @@
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>TaqMan</t>
-        </is>
-      </c>
-      <c r="AY2" t="n">
-        <v>100</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BA2" t="n">
-        <v>0.9399999999999999</v>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
@@ -1153,7 +1147,7 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1163,7 +1157,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>no (reported frequency only)</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1178,7 +1172,7 @@
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>Tableau IV: Tableau IV: Kribi urbain, Kdr West, N=100, R=0,94</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
@@ -1198,7 +1192,7 @@
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -1210,12 +1204,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>genotype</t>
+          <t>bioassay</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1225,7 +1219,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -1268,21 +1262,21 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Kribi urbain</t>
+          <t>Kribi rural</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>2.95</v>
+        <v>2.9167</v>
       </c>
       <c r="R3" t="n">
         <v>9.916700000000001</v>
@@ -1299,7 +1293,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -1329,7 +1323,7 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1347,63 +1341,53 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>permethrin</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>type I</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>WHO tube</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>synergist_preexposure</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+          <t>PBO</t>
+        </is>
+      </c>
+      <c r="AL3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>0.6875</v>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
@@ -1412,22 +1396,22 @@
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Vgsc</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>L995S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>L995S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
@@ -1437,24 +1421,28 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>TaqMan</t>
-        </is>
-      </c>
-      <c r="AY3" t="n">
-        <v>100</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BA3" t="n">
-        <v>0.18</v>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
@@ -1538,7 +1526,7 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1548,7 +1536,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>no (reported frequency only)</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1563,7 +1551,7 @@
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>Tableau IV: Tableau IV: Kribi urbain, Kdr East, N=100, R=0,18</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
@@ -1583,7 +1571,7 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -1595,7 +1583,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>genotype</t>
+          <t>bioassay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1610,7 +1598,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -1658,12 +1646,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q4" t="n">
@@ -1684,7 +1672,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1714,7 +1702,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1732,87 +1720,77 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>DDT</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>not a pyrethroid</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>WHO tube</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>diagnostic_dose</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="AL4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>77</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.9625</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>0.0375</v>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>confirmed resistance</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>Vgsc</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>L995F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>L995F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
@@ -1822,24 +1800,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>TaqMan</t>
-        </is>
-      </c>
-      <c r="AY4" t="n">
-        <v>75</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BA4" t="n">
-        <v>0.93</v>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
@@ -1923,7 +1905,7 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -1933,7 +1915,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>no (reported frequency only)</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -1948,7 +1930,7 @@
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>Tableau IV: Tableau IV: Kribi rural, Kdr West, N=75, R=0,93</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
@@ -1968,7 +1950,7 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -1980,7 +1962,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>genotype</t>
+          <t>bioassay</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1995,7 +1977,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -2043,12 +2025,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -2069,7 +2051,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -2099,7 +2081,7 @@
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2117,63 +2099,53 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>DDT</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>not a pyrethroid</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>60 min</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>WHO tube</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>synergist_preexposure</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+          <t>PBO</t>
+        </is>
+      </c>
+      <c r="AL5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.1875</v>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
@@ -2182,22 +2154,22 @@
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>24 h</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>Vgsc</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>L995S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>L995S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
@@ -2207,24 +2179,28 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>TaqMan</t>
-        </is>
-      </c>
-      <c r="AY5" t="n">
-        <v>75</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="BA5" t="n">
-        <v>0.15</v>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
@@ -2308,7 +2284,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2318,7 +2294,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>no (reported frequency only)</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2333,7 +2309,7 @@
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>Tableau IV: Tableau IV: Kribi rural, Kdr East, N=75, R=0,15</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
@@ -2353,7 +2329,7 @@
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2356,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -2428,12 +2404,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q6" t="n">
@@ -2454,7 +2430,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -2484,7 +2460,7 @@
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2502,17 +2478,17 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>permethrin</t>
+          <t>deltamethrin</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>type I</t>
+          <t>type II</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
@@ -2539,16 +2515,16 @@
         <v>80</v>
       </c>
       <c r="AM6" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="AN6" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.6375</v>
+        <v>0.325</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.3625</v>
+        <v>0.675</v>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
@@ -2687,7 +2663,7 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2697,7 +2673,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2712,7 +2688,7 @@
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Rurale, Perm. 75%: 36,25%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
@@ -2732,7 +2708,7 @@
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2735,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -2807,12 +2783,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q7" t="n">
@@ -2833,7 +2809,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -2863,7 +2839,7 @@
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -2881,17 +2857,17 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>permethrin</t>
+          <t>deltamethrin</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>type I</t>
+          <t>type II</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
@@ -2906,7 +2882,7 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>synergist_preexposure</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
@@ -2918,16 +2894,16 @@
         <v>80</v>
       </c>
       <c r="AM7" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="AN7" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.3125</v>
+        <v>0.15</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.6875</v>
+        <v>0.85</v>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
@@ -3066,7 +3042,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3076,7 +3052,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3091,7 +3067,7 @@
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Rurale, PBO + Perm. 75%: 68,75%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
@@ -3111,7 +3087,7 @@
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3104,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -3138,7 +3114,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3181,21 +3157,21 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Kribi rural</t>
+          <t>Kribi urbain</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>2.9167</v>
+        <v>2.95</v>
       </c>
       <c r="R8" t="n">
         <v>9.916700000000001</v>
@@ -3212,7 +3188,7 @@
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>town</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -3242,7 +3218,7 @@
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3260,17 +3236,17 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>DDT</t>
+          <t>permethrin</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>not a pyrethroid</t>
+          <t>type I</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
@@ -3297,16 +3273,16 @@
         <v>80</v>
       </c>
       <c r="AM8" t="n">
-        <v>77</v>
+        <v>45</v>
       </c>
       <c r="AN8" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.9625</v>
+        <v>0.5625</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.0375</v>
+        <v>0.4375</v>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
@@ -3445,7 +3421,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3455,7 +3431,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3470,7 +3446,7 @@
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Rurale, DDT 4%: 3,75%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
@@ -3490,7 +3466,7 @@
       </c>
       <c r="CA8" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3483,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -3517,7 +3493,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3560,21 +3536,21 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Kribi rural</t>
+          <t>Kribi urbain</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>2.9167</v>
+        <v>2.95</v>
       </c>
       <c r="R9" t="n">
         <v>9.916700000000001</v>
@@ -3591,7 +3567,7 @@
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>town</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -3621,7 +3597,7 @@
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3639,17 +3615,17 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>DDT</t>
+          <t>permethrin</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>not a pyrethroid</t>
+          <t>type I</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
@@ -3664,7 +3640,7 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>synergist_preexposure</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
@@ -3676,16 +3652,16 @@
         <v>80</v>
       </c>
       <c r="AM9" t="n">
-        <v>65</v>
+        <v>18</v>
       </c>
       <c r="AN9" t="n">
-        <v>15</v>
+        <v>62</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.8125</v>
+        <v>0.225</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.1875</v>
+        <v>0.775</v>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
@@ -3824,7 +3800,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -3834,7 +3810,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -3849,7 +3825,7 @@
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Rurale, PBO+ DDT 4%: 18,75%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
@@ -3869,7 +3845,7 @@
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -3886,7 +3862,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -3896,7 +3872,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3939,21 +3915,21 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Kribi rural</t>
+          <t>Kribi urbain</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>2.9167</v>
+        <v>2.95</v>
       </c>
       <c r="R10" t="n">
         <v>9.916700000000001</v>
@@ -3970,7 +3946,7 @@
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>town</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -4000,7 +3976,7 @@
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4018,17 +3994,17 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>deltamethrin</t>
+          <t>DDT</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>type II</t>
+          <t>not a pyrethroid</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -4055,16 +4031,16 @@
         <v>80</v>
       </c>
       <c r="AM10" t="n">
-        <v>26</v>
+        <v>75</v>
       </c>
       <c r="AN10" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.325</v>
+        <v>0.9375</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.675</v>
+        <v>0.0625</v>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
@@ -4203,7 +4179,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4213,7 +4189,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4228,7 +4204,7 @@
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Rurale, Delta. 0,05%: 67,5%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
@@ -4248,7 +4224,7 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -4265,7 +4241,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -4275,7 +4251,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -4318,21 +4294,21 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>Kribi rural</t>
+          <t>Kribi urbain</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>2.9167</v>
+        <v>2.95</v>
       </c>
       <c r="R11" t="n">
         <v>9.916700000000001</v>
@@ -4349,7 +4325,7 @@
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>village</t>
+          <t>town</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -4379,7 +4355,7 @@
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4397,17 +4373,17 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>deltamethrin</t>
+          <t>DDT</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>type II</t>
+          <t>not a pyrethroid</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
@@ -4422,7 +4398,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>synergist_preexposure</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
@@ -4434,17 +4410,17 @@
         <v>80</v>
       </c>
       <c r="AM11" t="n">
+        <v>68</v>
+      </c>
+      <c r="AN11" t="n">
         <v>12</v>
       </c>
-      <c r="AN11" t="n">
-        <v>68</v>
-      </c>
       <c r="AO11" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AP11" t="n">
         <v>0.15</v>
       </c>
-      <c r="AP11" t="n">
-        <v>0.85</v>
-      </c>
       <c r="AQ11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -4582,7 +4558,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -4592,7 +4568,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -4607,7 +4583,7 @@
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Rurale, PBO + Delta. 0,05%: 85%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
@@ -4627,7 +4603,7 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -4654,7 +4630,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -4702,12 +4678,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q12" t="n">
@@ -4758,7 +4734,7 @@
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -4776,17 +4752,17 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>permethrin</t>
+          <t>deltamethrin</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>type I</t>
+          <t>type II</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
@@ -4813,16 +4789,16 @@
         <v>80</v>
       </c>
       <c r="AM12" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="AN12" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.5625</v>
+        <v>0.4125</v>
       </c>
       <c r="AP12" t="n">
-        <v>0.4375</v>
+        <v>0.5875</v>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
@@ -4961,7 +4937,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -4971,7 +4947,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -4986,7 +4962,7 @@
       </c>
       <c r="BW12" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Urbaine, Perm. 75%: 43,75%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX12" t="inlineStr">
@@ -5006,7 +4982,7 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5009,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -5081,12 +5057,12 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q13" t="n">
@@ -5137,7 +5113,7 @@
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5155,17 +5131,17 @@
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>permethrin</t>
+          <t>deltamethrin</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>type I</t>
+          <t>type II</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
@@ -5180,7 +5156,7 @@
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>synergist_preexposure</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
@@ -5192,16 +5168,16 @@
         <v>80</v>
       </c>
       <c r="AM13" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="AN13" t="n">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="AO13" t="n">
-        <v>0.225</v>
+        <v>0.1</v>
       </c>
       <c r="AP13" t="n">
-        <v>0.775</v>
+        <v>0.9</v>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
@@ -5340,7 +5316,7 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
@@ -5350,7 +5326,7 @@
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5365,7 +5341,7 @@
       </c>
       <c r="BW13" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Urbaine, PBO + Perm. 75%: 77,5%</t>
+          <t>Tableau III: Tableau III: Mortalités (%) des femelles d’An. gambiae s.l. (souches rurale, urbaine, Kisumu) obtenues après 24h d’observation</t>
         </is>
       </c>
       <c r="BX13" t="inlineStr">
@@ -5385,7 +5361,7 @@
       </c>
       <c r="CA13" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5373,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>bioassay</t>
+          <t>geno_pheno</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -5412,7 +5388,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -5460,12 +5436,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q14" t="n">
@@ -5516,7 +5492,7 @@
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -5534,72 +5510,82 @@
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>DDT</t>
+          <t>DDT, permethrin, deltamethrin</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>not a pyrethroid</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>WHO tube</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AL14" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.9375</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>0.0625</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>confirmed resistance</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Vgsc</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995F</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -5669,12 +5655,12 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995F</t>
         </is>
       </c>
       <c r="BJ14" t="inlineStr">
@@ -5719,7 +5705,7 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
@@ -5729,7 +5715,7 @@
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no (reported allele frequency only: survivors 0.94)</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -5744,7 +5730,7 @@
       </c>
       <c r="BW14" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Urbaine, DDT 4%: 6,25%</t>
+          <t>Tableau IV: Tableau IV: Fréquences alléliques des mutations Kdr chez les échantillons d’An. gambiae s.l de Kribi</t>
         </is>
       </c>
       <c r="BX14" t="inlineStr">
@@ -5764,7 +5750,7 @@
       </c>
       <c r="CA14" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>survivors/dead pooled across tests — not linked to a single bioassay</t>
         </is>
       </c>
     </row>
@@ -5776,7 +5762,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>bioassay</t>
+          <t>geno_pheno</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -5791,7 +5777,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -5839,12 +5825,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 2</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -5895,7 +5881,7 @@
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -5913,53 +5899,63 @@
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>DDT</t>
+          <t>DDT, permethrin, deltamethrin</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>not a pyrethroid</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>WHO tube</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>PBO</t>
-        </is>
-      </c>
-      <c r="AL15" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM15" t="n">
-        <v>68</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO15" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AP15" t="n">
-        <v>0.15</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
@@ -5968,17 +5964,17 @@
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Vgsc</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995S</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6048,12 +6044,12 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995S</t>
         </is>
       </c>
       <c r="BJ15" t="inlineStr">
@@ -6098,7 +6094,7 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
@@ -6108,7 +6104,7 @@
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no (reported allele frequency only: survivors 0.18)</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6123,7 +6119,7 @@
       </c>
       <c r="BW15" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Urbaine, PBO+ DDT 4%: 15%</t>
+          <t>Tableau IV: Tableau IV: Fréquences alléliques des mutations Kdr chez les échantillons d’An. gambiae s.l de Kribi</t>
         </is>
       </c>
       <c r="BX15" t="inlineStr">
@@ -6143,7 +6139,7 @@
       </c>
       <c r="CA15" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>survivors/dead pooled across tests — not linked to a single bioassay</t>
         </is>
       </c>
     </row>
@@ -6155,12 +6151,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>bioassay</t>
+          <t>geno_pheno</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -6170,7 +6166,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -6213,21 +6209,21 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>Kribi urbain</t>
+          <t>Kribi rural</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>2.95</v>
+        <v>2.9167</v>
       </c>
       <c r="R16" t="n">
         <v>9.916700000000001</v>
@@ -6244,7 +6240,7 @@
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -6274,7 +6270,7 @@
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -6292,72 +6288,82 @@
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>deltamethrin</t>
+          <t>DDT, permethrin, deltamethrin</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>type II</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>WHO tube</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="AL16" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>33</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>47</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>0.4125</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>0.5875</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>confirmed resistance</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Vgsc</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995F</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -6427,12 +6433,12 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995F</t>
         </is>
       </c>
       <c r="BJ16" t="inlineStr">
@@ -6477,7 +6483,7 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
@@ -6487,7 +6493,7 @@
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no (reported allele frequency only: survivors 0.93)</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -6502,7 +6508,7 @@
       </c>
       <c r="BW16" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Urbaine, Delta. 0,05%: 58,75%</t>
+          <t>Tableau IV: Tableau IV: Fréquences alléliques des mutations Kdr chez les échantillons d’An. gambiae s.l de Kribi</t>
         </is>
       </c>
       <c r="BX16" t="inlineStr">
@@ -6522,7 +6528,7 @@
       </c>
       <c r="CA16" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>survivors/dead pooled across tests — not linked to a single bioassay</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6540,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>bioassay</t>
+          <t>geno_pheno</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>isabelleborloz__5362_NTONGA_AKONO_urban</t>
+          <t>isabelleborloz__5362_NTONGA_AKONO_rural</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -6549,7 +6555,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>36815176</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -6592,21 +6598,21 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>Kribi urbain</t>
+          <t>Kribi rural</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>South Region</t>
+          <t>South</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Kribi 1</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>2.95</v>
+        <v>2.9167</v>
       </c>
       <c r="R17" t="n">
         <v>9.916700000000001</v>
@@ -6623,7 +6629,7 @@
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>town</t>
+          <t>admin2</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -6653,7 +6659,7 @@
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>larvae</t>
+          <t>adults</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -6671,53 +6677,63 @@
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>deltamethrin</t>
+          <t>DDT, permethrin, deltamethrin</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>type II</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>WHO tube</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>diagnostic_dose</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>PBO</t>
-        </is>
-      </c>
-      <c r="AL17" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>8</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>72</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>0.9</v>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
@@ -6726,17 +6742,17 @@
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>24 h</t>
+          <t>NA</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>Vgsc</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995S</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -6806,12 +6822,12 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>alive</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>L995S</t>
         </is>
       </c>
       <c r="BJ17" t="inlineStr">
@@ -6856,7 +6872,7 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>morphological and PCR</t>
+          <t>PCR</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
@@ -6866,7 +6882,7 @@
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no (reported allele frequency only: survivors 0.15)</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -6881,7 +6897,7 @@
       </c>
       <c r="BW17" t="inlineStr">
         <is>
-          <t>Tableau III: Tableau III: Urbaine, PBO + Delta. 0,05%: 90%</t>
+          <t>Tableau IV: Tableau IV: Fréquences alléliques des mutations Kdr chez les échantillons d’An. gambiae s.l de Kribi</t>
         </is>
       </c>
       <c r="BX17" t="inlineStr">
@@ -6901,7 +6917,7 @@
       </c>
       <c r="CA17" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>survivors/dead pooled across tests — not linked to a single bioassay</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6944,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>33557825</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -6951,7 +6967,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Anopheles gambiae sensu stricto (s.s.)</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -6961,7 +6977,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>An. gambiae s.s.</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7027,7 +7043,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>indoor aspiration</t>
+          <t>aspiration of blood fed and gravid mosquitoes</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -7037,7 +7053,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>wild_reared</t>
+          <t>f1_progeny</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -7140,7 +7156,7 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>1014S</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
@@ -7251,7 +7267,7 @@
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>no (reported frequency only)</t>
+          <t>no (reported frequency only; carriers 99/100)</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -7266,12 +7282,12 @@
       </c>
       <c r="BW18" t="inlineStr">
         <is>
-          <t>Of all 100 samples, 99% had the kdr east (Vgsc_1014S) mutation and the remaining one had the kdr west (Vgsc_1014F) gene mutation... along with high frequency (99.14%) of the kdr east allele in the F1 progeny originating from Tulukuyi, Western Kenya.</t>
+          <t>Of all 100 samples, 99% had the kdr east (Vgsc_1014S) mutation and the remaining one had the kdr west (Vgsc_1014F) gene mutation. This high frequency of kdr east mutation indicated fixation in the mosquito population and thus precluded further correlation analysis between microbial composition and kdr allele frequencies.</t>
         </is>
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>6, 8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
@@ -7313,7 +7329,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>33557825</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -7336,7 +7352,7 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Anopheles gambiae sensu stricto (s.s.)</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -7346,7 +7362,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>An. gambiae s.s.</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -7412,7 +7428,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>indoor aspiration</t>
+          <t>aspiration of blood fed and gravid mosquitoes</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -7422,7 +7438,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>wild_reared</t>
+          <t>f1_progeny</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -7525,7 +7541,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>1014F</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -7541,8 +7557,10 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="BA19" t="n">
-        <v>0.01</v>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
@@ -7636,7 +7654,7 @@
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>no (reported frequency only)</t>
+          <t>carriers only (1/100) — allele frequency not determinable</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -7651,12 +7669,12 @@
       </c>
       <c r="BW19" t="inlineStr">
         <is>
-          <t>Post bioassay, 50 resistant and 50 susceptible mosquitoes were subsequently screened for kdr East and West mutations... of the 100 selected for further processing, 99% were positive for kdr East and 1% for kdr West... and the remaining one had the kdr west (Vgsc_1014F) gene mutation.</t>
+          <t>Of all 100 samples, 99% had the kdr east (Vgsc_1014S) mutation and the remaining one had the kdr west (Vgsc_1014F) gene mutation.</t>
         </is>
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>1, 6</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
@@ -7698,7 +7716,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>33557825</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -7721,7 +7739,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Anopheles gambiae sensu stricto (s.s.)</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -7731,7 +7749,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>An. gambiae s.s.</t>
+          <t>Anopheles gambiae s.s.</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -7797,7 +7815,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>indoor aspiration</t>
+          <t>aspiration of blood fed and gravid mosquitoes</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -7807,7 +7825,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>wild_reared</t>
+          <t>f1_progeny</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -7840,12 +7858,12 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>CDC bottle</t>
+          <t>CDC bottle bioassay</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>intensity</t>
+          <t>intensity bioassay</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
@@ -8015,7 +8033,7 @@
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>derived (reported % x n)</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8030,12 +8048,12 @@
       </c>
       <c r="BW20" t="inlineStr">
         <is>
-          <t>A total of 133 F1 virgin, non-blood fed adult females aged 2–3days were tested for permethrin resistance following the Centers for Disease Control and Prevention (CDC) guidelines for evaluating insecticide resistance [24]... at a final concentration of 107.5µg/ml (5× the dose for discriminating permethrin resistance in Anopheles)... Using the F1 progeny, the bioassays were conducted for 30 minutes at the end of which permethrin resistance was recorded. Mosquitoes that were alive after the bioassay were categorized as resistant and subsequently killed by freezing, while those that were dead or moribund were categorized as susceptible. (Page 4); A total of 133 adult F1 female An. gambiae s.s. were tested for resistance to permethrin using 5× (107.5 µg/ml) the discriminating dose (21.5 µg/ml) of the insecticide, and 52.6% of the samples tested were found to be susceptible. (Page 6)</t>
+          <t>A total of 133 F1 virgin, non-blood fed adult females aged 2–3days were tested for permethrin resistance following the Centers for Disease Control and Prevention (CDC) guidelines for evaluating insecticide resistance [24]... Using the F1 progeny, the bioassays were conducted for 30 minutes at the end of which permethrin resistance was recorded. Mosquitoes that were alive after the bioassay were categorized as resistant and subsequently killed by freezing, while those that were dead or moribund were categorized as susceptible.</t>
         </is>
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>4, 6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
@@ -8050,7 +8068,7 @@
       </c>
       <c r="CA20" t="inlineStr">
         <is>
-          <t>NA</t>
+          <t>dead/surviving counts derived in code from reported % x number exposed</t>
         </is>
       </c>
     </row>
